--- a/reference/origins/product info/Concentrate Final Product List for WA.xlsx
+++ b/reference/origins/product info/Concentrate Final Product List for WA.xlsx
@@ -632,7 +632,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>Constellation Cannabis</x:v>
+        <x:v>Constellation</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
         <x:v>Trop Cherry</x:v>
@@ -1217,7 +1217,7 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="10" t="str">
-        <x:v>Constellation Cannabis</x:v>
+        <x:v>Constellation</x:v>
       </x:c>
       <x:c r="C19" s="10" t="str">
         <x:v>Harlequin</x:v>
@@ -1802,7 +1802,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="10" t="str">
-        <x:v>Constellation Cannabis</x:v>
+        <x:v>Constellation</x:v>
       </x:c>
       <x:c r="C32" s="10" t="str">
         <x:v>Blue Dream</x:v>
@@ -2387,7 +2387,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="10" t="str">
-        <x:v>Constellation Cannabis</x:v>
+        <x:v>Constellation</x:v>
       </x:c>
       <x:c r="C45" s="10" t="str">
         <x:v>Purple Punch</x:v>
